--- a/SHOP_Qcut_單筆交易餘額占比.xlsx
+++ b/SHOP_Qcut_單筆交易餘額占比.xlsx
@@ -413,36 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>SHAP_Min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SHAP_Max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Feature_Mean</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SHAP_Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SHAP_Median</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SHAP_Std</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Fraud_Prob</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cnt</t>
         </is>
@@ -450,201 +460,261 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>-1.637599945068359</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.4038999974727631</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.0999</v>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>-0.271699994802475</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>-0.2750999927520752</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.335999995470047</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>0.864300012588501</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1411</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>-0.2041999995708466</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.4560000002384186</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.2446</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>0.1165999993681908</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>0.1096000000834465</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.0957999974489212</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.8680999875068665</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>-0.05590000003576279</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4630999863147736</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.3915</v>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>0.1806000024080276</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>0.1773999929428101</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>0.07689999788999557</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.8661999702453613</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>0.02740000002086163</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.4510000050067902</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.5662</v>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>0.2153999954462051</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>0.2108999937772751</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.0681999996304512</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>0.866599977016449</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>0.09549999982118607</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5827999711036682</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.7786999999999999</v>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>0.2666999995708466</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>0.2531999945640564</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>0.08380000293254852</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>0.8632000088691711</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>0.151199996471405</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6739000082015991</v>
+      </c>
+      <c r="C7" t="n">
         <v>0.9351</v>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>0.3752000033855438</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>0.367000013589859</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.08579999953508377</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>0.8637999892234802</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>-0.04100000113248825</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.7268000245094299</v>
+      </c>
+      <c r="C8" t="n">
         <v>0.9984</v>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>0.3953000009059906</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>0.3864000141620636</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>0.09369999915361404</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>0.8619999885559082</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>0.0706000030040741</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.199200034141541</v>
+      </c>
+      <c r="C9" t="n">
         <v>3.8615</v>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>0.3655999898910522</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>0.3461999893188477</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>0.1234999969601631</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>0.8641999959945679</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>0.2296999990940094</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.463899970054626</v>
+      </c>
+      <c r="C10" t="n">
         <v>29.0525</v>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>0.651199996471405</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>0.6482999920845032</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>0.13230000436306</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>0.8629999756813049</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>0.003299999982118607</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2.282299995422363</v>
+      </c>
+      <c r="C11" t="n">
         <v>8215.6216</v>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>0.6689000129699707</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>0.6780999898910522</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>0.1731999963521957</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>0.8679999709129333</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>1411</v>
       </c>
     </row>
